--- a/dados/excel/salarios_por_perfil.xlsx
+++ b/dados/excel/salarios_por_perfil.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$E$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,6 +127,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -134,6 +137,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -582,7 +588,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -603,7 +609,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>vírgula</t>
+          <t>ponto e vírgula</t>
         </is>
       </c>
     </row>
@@ -627,7 +633,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -658,24 +664,24 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>dimensao</t>
+          <t>﻿escolaridade_canonica</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Número decimal (#,##0,00)</t>
+          <t>Texto</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>faixa_tempo</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -755,25 +761,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>dimensao</t>
+          <t>﻿escolaridade_canonica</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>faixa_tempo</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
@@ -795,362 +801,740 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>escolaridade</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
           <t>Sem escolaridade formal registrada</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="D2" s="10" t="n">
-        <v>4286.16</v>
-      </c>
-      <c r="E2" s="10" t="n">
-        <v>3745.37</v>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>5 a 10 anos</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>3495.325</v>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>3495.325</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>escolaridade</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Fundamental incompleto</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>5781.82</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>5316.73</v>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Sem escolaridade formal registrada</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>10 a 20 anos</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="15" t="n">
+        <v>3671.31</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>3671.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>escolaridade</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Fundamental completo</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>280</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>5371.49</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>4614.73</v>
+          <t>Sem escolaridade formal registrada</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>20+ anos</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>4679.917142857144</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>4200.96</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>escolaridade</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Medio incompleto</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>6769.56</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>5543.02</v>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Fundamental incompleto</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>5 a 10 anos</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>4695.726666666666</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>5082.969999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>escolaridade</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Medio completo</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>3592</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>5858.13</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>5194.78</v>
+          <t>Fundamental incompleto</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>10 a 20 anos</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>5240.609166666666</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>5053.315000000001</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>escolaridade</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Superior incompleto</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>934</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>2182.01</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>1084.8</v>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Fundamental incompleto</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>20+ anos</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>6089.755714285715</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>5825.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>escolaridade</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Superior completo</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>6887</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>8604.52</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>7478.65</v>
+          <t>Fundamental completo</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>1 a 5 anos</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>4102.129545454546</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>3725.13</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>escolaridade</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Pos-graduacao</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>1898</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>15811.58</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>14133.37</v>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Fundamental completo</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>5 a 10 anos</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>4808.2053125</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>4565.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>escolaridade</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Mestrado</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>110</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>21657.42</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>17931.19</v>
+          <t>Fundamental completo</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>10 a 20 anos</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>5239.949206349206</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>5167.26</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>escolaridade</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Doutorado</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>22573.96</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>21133.89</v>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Fundamental completo</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>20+ anos</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>97</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>6545.758969072165</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>5554.17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>tempo_casa</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>0-5 anos</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>5410</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>5812.81</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>4599.99</v>
+          <t>Medio incompleto</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>10 a 20 anos</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>6330.077499999999</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>5252.6</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>tempo_casa</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>6-10 anos</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>1894</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>7176.19</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>5579.04</v>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Medio incompleto</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>20+ anos</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>8399.477999999999</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>8206.775</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>tempo_casa</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>11-15 anos</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>3284</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>9289.629999999999</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>7602.6</v>
+          <t>Medio completo</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>1 a 5 anos</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>1803</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>5112.002201885746</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>4760.41</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>tempo_casa</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>16-20 anos</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>1858</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>12754.86</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>11819.19</v>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Medio completo</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>5 a 10 anos</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>430</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>4858.009651162791</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>4539.309999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>tempo_casa</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>21-25 anos</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>760</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>13261.67</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>12999.53</v>
+          <t>Medio completo</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>10 a 20 anos</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>1063</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>6105.019426152399</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>5482.39</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>tempo_casa</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>26-30 anos</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>181</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>15488.92</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>15685.39</v>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Medio completo</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>20+ anos</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>327</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>10662.17339449541</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>9589.799999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>tempo_casa</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>30+ anos</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>378</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>13764.24</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>11123.51</v>
+          <t>Superior incompleto</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>1 a 5 anos</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>361</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>1192.82243767313</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>1084.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Superior incompleto</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>5 a 10 anos</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>204</v>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>1832.467549019608</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>1084.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Superior incompleto</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>10 a 20 anos</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>352</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>3508.779403409091</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Superior incompleto</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>20+ anos</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>7872.676388888888</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>6794.03</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Superior completo</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>1 a 5 anos</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>2798</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>6084.097991422444</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>4876.53</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Superior completo</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>5 a 10 anos</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>1238</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>8464.364789983845</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>8010.13</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Superior completo</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>10 a 20 anos</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>2674</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>10116.01635751683</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>8892.555</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Superior completo</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>20+ anos</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>590</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>13696.63896610169</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>11987.83</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Pos-graduacao</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>1 a 5 anos</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>7755.433921568628</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>6759.66</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Pos-graduacao</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>5 a 10 anos</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>141</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>10652.58106382979</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>10646.81</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Pos-graduacao</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>10 a 20 anos</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>1378</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>15481.47550798258</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>13837.58</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Pos-graduacao</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>20+ anos</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>364</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>18805.45445054945</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>19257.29</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Mestrado</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>1 a 5 anos</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>11310.91</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>11310.91</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Mestrado</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>5 a 10 anos</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>15384.87818181818</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>15641.92</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Mestrado</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>10 a 20 anos</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>20736.32447368421</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>17849.425</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Mestrado</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>20+ anos</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>23476.62055555555</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>20776.165</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>5 a 10 anos</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>17899.63333333334</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>16261</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>10 a 20 anos</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>21444.655</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>20599.325</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Doutorado</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>20+ anos</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>26676.66125</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>29674.82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E18"/>
+  <autoFilter ref="A1:E36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>